--- a/rules/CORE-000137/negative/02/data/unit-test-coreid-CG0100-negative 2.xlsx
+++ b/rules/CORE-000137/negative/02/data/unit-test-coreid-CG0100-negative 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\core-contributor\rules\CORE-000137\negative\02\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC371658-D3B3-4EEE-AEB8-4141B2533498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6E1CA4-123E-4B44-A2B5-05D974B5A97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="99">
   <si>
     <t>Product</t>
   </si>
@@ -771,7 +771,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1022,6 +1022,80 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2307,9 +2381,11 @@
       <c r="G20" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I20" s="6">
+      <c r="H20" s="8"/>
+      <c r="I20" s="9">
         <v>-5</v>
       </c>
+      <c r="J20" s="8"/>
       <c r="K20" s="5" t="s">
         <v>67</v>
       </c>
